--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>43319</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43348</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>43374</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>43409</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>43413</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43413</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>43415</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43415</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>43418</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>43419</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>43420</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43420</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>43423</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>43423</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>43425</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>43431</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>43432</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>43432</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>43433</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>43433</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>43437</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>43437</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>43441</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>43441</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>43445</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>43447</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>43447</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>43454</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>43467</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>43467</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>43468</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>43468</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>43472</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>43472</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>43473</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>43473</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>43475</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>43475</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>43479</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>43479</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>43503</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>43505</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>43516</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>43516</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43524</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43528</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>43535</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>43536</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>43536</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>43542</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>43542</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43545</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43545</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43549</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43549</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43550</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43550</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43552</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43552</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43553</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43557</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43558</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43558</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43563</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43564</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>43564</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>43565</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>43566</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>43570</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>43573</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>43581</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>43587</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43606</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43612</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43612</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43616</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43619</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43620</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43620</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43656</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43658</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43663</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43664</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43665</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43665</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>43682</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>43682</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43689</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>43705</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>43706</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>43712</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>43712</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>43731</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>43731</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>43732</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>43732</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43738</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43739</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43739</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>43741</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>43742</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>43742</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>43768</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>43770</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>43774</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>43775</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>43775</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43790</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43796</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43803</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>43837</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>43837</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>43839</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>43839</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>43846</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>43850</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>43852</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>43854</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>43858</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>43859</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>43871</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>43875</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>43880</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>43880</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>43901</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>43901</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>43903</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>43908</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>43913</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>43916</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43927</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43936</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43937</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43937</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43941</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43943</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43943</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43949</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43957</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43966</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43969</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43983</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>44000</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>44007</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44019</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44020</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>44020</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>44021</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>44022</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>44022</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44025</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44028</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>44036</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>44039</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44041</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>44041</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44043</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44046</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44055</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44060</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44062</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44085</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44088</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44092</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44095</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44095</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44103</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44107</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44107</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44122</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44122</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44123</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44123</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44124</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44133</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44133</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44140</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44140</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44141</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>44144</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>44145</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44146</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44146</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>44147</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>44147</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44154</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44159</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44159</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44162</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44166</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44168</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>44172</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>44173</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>44174</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44174</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44177</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44177</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>44180</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>44187</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44193</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>44199</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44210</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44216</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44224</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44230</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44230</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44231</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44236</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44236</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44238</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44242</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44243</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44245</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44245</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44250</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44250</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44251</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44256</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44261</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>44263</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44263</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>44265</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>44266</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44266</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>44267</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>44267</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44274</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44274</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44277</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44277</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44278</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44281</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44293</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44295</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44298</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44298</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44302</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44302</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44306</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44307</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44321</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44322</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44322</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44323</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44332</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>44333</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44335</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44335</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>44336</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>44336</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44341</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>44347</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44356</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44356</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44357</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44357</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44363</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>44363</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>44365</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44371</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44371</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>44373</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>44375</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>44375</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>44376</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44378</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>44384</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44384</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44389</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44396</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44405</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>44407</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44421</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44427</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44442</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44446</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44448</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44449</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44454</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44454</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>44455</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44455</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44456</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>44460</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>44460</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44469</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>44469</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>44475</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>44475</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>44476</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>44476</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>44477</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44477</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44480</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>44481</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>44481</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>44482</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>44482</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>44483</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44483</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>44487</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>44487</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>44488</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>44488</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44489</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>44489</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>44494</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>44495</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>44495</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>44498</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44500</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>44501</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>44502</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>44505</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44508</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>44510</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>44515</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>44523</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>44529</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>44530</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44532</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>44539</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44557</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44557</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>44559</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44559</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44573</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44573</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44575</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44578</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44592</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44592</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>44596</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44600</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44600</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44601</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44607</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44613</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44615</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44617</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44621</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>44624</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>44624</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>44631</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44634</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44635</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44637</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44638</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44641</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44644</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>44644</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>44648</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>44651</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44651</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>44655</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>44659</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44659</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44671</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44692</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44693</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44694</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44694</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44697</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44699</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44701</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44701</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>44705</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44705</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>44711</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>44711</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>44712</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>44712</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>44714</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>44714</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>44726</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>44727</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44729</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>44735</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>44735</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>44739</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>44739</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>44750</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>44753</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>44756</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44756</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>44757</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44762</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44763</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>44770</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>44770</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>44777</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>44778</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>44778</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>44795</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44796</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44796</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44797</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>44801</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>44810</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44812</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>44813</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44813</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>44817</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44818</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>44823</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>44823</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>44826</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>44827</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>44830</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44830</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>44834</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44834</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44839</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44845</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>44847</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44847</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>44851</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>44851</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44855</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44865</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>44865</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>44866</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>44867</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>44868</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>44868</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>44869</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>44872</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>44872</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>44873</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>44876</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44876</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>44883</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>44887</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>44889</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>44893</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>44893</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>44896</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>44896</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>44899</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>44900</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>44900</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>44901</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>44903</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>44903</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44907</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>44910</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44914</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>44917</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34683,7 +34683,7 @@
         <v>44926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>44926</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44931</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44950</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44951</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44953</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44958</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44958</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44964</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>44964</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>44965</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44967</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44970</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44970</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44974</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>44974</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>44980</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>44981</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>44990</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>44995</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>44995</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>44999</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44999</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45002</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45002</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45013</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45014</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45020</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45027</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>45027</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45028</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>45030</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45030</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>45035</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45035</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>45037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45040</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45042</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45044</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>45051</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>45051</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45061</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45061</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45062</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45062</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>45063</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45070</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45075</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>45075</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45084</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45084</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>45085</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45086</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45089</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45091</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45091</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45092</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45092</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45096</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45097</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45097</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45098</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45098</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>45099</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45104</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45104</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>45107</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45107</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45109</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>45109</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45110</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45110</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45114</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45117</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45118</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>45126</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>45128</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>45131</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>45132</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>45132</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>45149</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>45153</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45153</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>45154</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>45155</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>45155</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45159</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45159</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>45162</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>45162</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>45163</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45163</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>45166</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>45167</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>45167</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>45168</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>45168</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>45169</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45169</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45170</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>45170</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>45173</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45176</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45176</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>45181</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45182</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45182</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>45186</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45190</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>45190</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45194</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45194</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45198</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45199</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45199</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45203</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45204</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45204</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45205</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45205</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45211</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45211</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45212</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45218</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45222</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45222</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45223</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45225</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45225</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45226</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45229</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45229</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45230</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45233</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45236</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45238</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45238</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45243</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45244</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45245</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45245</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45246</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45250</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45251</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45252</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45257</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45258</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45259</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45260</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45265</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45267</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45268</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45271</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45272</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45274</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45278</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45279</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>45281</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45287</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45288</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45293</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45295</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45299</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45300</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45301</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>45307</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45309</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45310</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>45314</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         <v>45315</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50369,14 +50369,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 3132-2024</t>
+          <t>A 3126-2024</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -50426,14 +50426,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 3037-2024</t>
+          <t>A 3122-2024</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -50488,14 +50488,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 3122-2024</t>
+          <t>A 3037-2024</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -50550,14 +50550,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 3126-2024</t>
+          <t>A 3132-2024</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -50607,14 +50607,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 4528-2024</t>
+          <t>A 4523-2024</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -50664,14 +50664,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 4523-2024</t>
+          <t>A 4527-2024</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -50721,14 +50721,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 4527-2024</t>
+          <t>A 4528-2024</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -50785,7 +50785,7 @@
         <v>45328</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>45329</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>45330</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45331</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45334</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>43319</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43348</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>43374</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>43409</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>43413</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43413</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>43415</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43415</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>43418</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>43419</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>43420</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43420</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>43423</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>43423</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>43425</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>43431</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>43432</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>43432</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>43433</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>43433</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>43437</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>43437</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>43441</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>43441</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>43445</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>43447</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>43447</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>43454</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>43467</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>43467</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>43468</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>43468</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>43472</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>43472</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>43473</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>43473</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>43475</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>43475</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>43479</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>43479</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>43503</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>43505</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>43516</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>43516</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43524</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43528</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>43535</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>43536</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>43536</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>43542</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>43542</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43545</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43545</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43549</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43549</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43550</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43550</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43552</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43552</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43553</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43557</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43558</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43558</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43563</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43564</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>43564</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>43565</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>43566</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>43570</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>43573</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>43581</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>43587</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>43606</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>43612</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>43612</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>43616</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43619</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43620</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43620</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43656</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43658</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43663</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43664</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43665</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43665</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>43682</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>43682</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43689</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>43705</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>43706</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>43712</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>43712</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>43731</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>43731</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>43732</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>43732</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43738</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43739</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43739</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>43741</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>43742</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>43742</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>43768</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>43770</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>43774</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>43775</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>43775</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43790</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43796</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43803</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>43837</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>43837</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>43839</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>43839</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>43846</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>43850</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>43852</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>43854</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>43858</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>43859</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>43871</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>43875</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>43880</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>43880</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>43901</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>43901</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>43903</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>43908</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>43913</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>43916</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43927</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43936</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43937</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43937</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43941</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43943</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43943</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43949</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43957</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43966</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43969</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43983</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>44000</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>44007</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44019</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44020</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>44020</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>44021</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>44022</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>44022</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44025</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44028</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>44036</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>44039</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44041</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>44041</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44043</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44046</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44055</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44060</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44062</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44085</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44088</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44092</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44095</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44095</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44103</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44107</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44107</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44122</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44122</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44123</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44123</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44124</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44133</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44133</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44140</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44140</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44141</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>44144</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>44145</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44146</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44146</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>44147</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>44147</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44154</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44159</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44159</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44162</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44166</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44168</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>44172</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>44173</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>44174</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44174</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44177</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44177</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>44180</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>44187</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44193</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>44199</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44210</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44216</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44224</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44230</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44230</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44231</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44236</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44236</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44238</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44242</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44243</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44245</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44245</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44250</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44250</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44251</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44256</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44261</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>44263</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44263</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>44265</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>44266</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44266</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>44267</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>44267</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44274</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44274</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44277</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44277</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44278</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44281</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44293</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44295</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44298</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44298</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44302</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44302</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44306</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44307</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44321</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44322</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44322</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44323</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44332</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>44333</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44335</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44335</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>44336</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>44336</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44341</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>44347</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44356</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44356</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44357</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44357</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44363</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>44363</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>44365</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44371</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44371</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>44373</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>44375</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>44375</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>44376</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44378</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>44384</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44384</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44389</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44396</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44405</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>44407</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44421</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44427</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44442</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44446</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44448</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44449</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44454</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44454</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>44455</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44455</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44456</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>44460</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>44460</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44469</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>44469</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>44475</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>44475</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>44476</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>44476</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>44477</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44477</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44480</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>44481</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>44481</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>44482</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>44482</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>44483</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44483</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>44487</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>44487</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>44488</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>44488</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44489</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>44489</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>44494</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>44495</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>44495</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>44498</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44500</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>44501</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>44502</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>44505</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44508</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>44510</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>44515</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>44523</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>44529</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>44530</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44532</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>44539</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44557</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44557</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>44559</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44559</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44573</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44573</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44575</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44578</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44592</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44592</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>44596</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44600</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44600</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44601</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44607</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44613</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44615</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44617</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44621</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>44624</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>44624</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>44631</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44634</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44635</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44637</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44638</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44641</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44644</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>44644</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>44648</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>44651</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44651</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>44655</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>44659</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44659</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44671</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44692</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44693</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44694</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44694</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44697</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44699</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44701</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44701</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>44705</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44705</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>44711</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>44711</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>44712</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>44712</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>44714</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>44714</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>44726</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>44727</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44729</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>44735</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>44735</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>44739</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>44739</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>44750</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>44753</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>44756</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>44756</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>44757</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44762</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44763</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>44770</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>44770</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>44777</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>44778</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>44778</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>44795</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44796</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44796</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44797</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>44801</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>44810</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44812</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>44813</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44813</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>44817</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44818</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>44823</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>44823</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>44826</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>44827</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>44830</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44830</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>44834</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44834</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44839</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44845</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>44847</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44847</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>44851</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>44851</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44855</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44865</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>44865</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>44866</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>44867</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>44868</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>44868</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>44869</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>44872</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>44872</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>44873</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>44876</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44876</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>44883</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>44887</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>44889</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>44893</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>44893</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>44896</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>44896</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>44899</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>44900</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>44900</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>44901</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>44903</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>44903</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44907</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>44910</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44914</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>44917</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34683,7 +34683,7 @@
         <v>44926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>44926</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44931</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44950</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44951</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44953</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44958</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44958</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>44964</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>44964</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>44965</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>44967</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44970</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44970</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44974</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>44974</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>44980</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>44981</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>44990</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>44995</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>44995</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>44999</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44999</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45002</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45002</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45013</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45014</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>45019</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45019</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45020</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45027</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>45027</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45028</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>45030</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45030</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>45035</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45035</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>45037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45040</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45042</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45044</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>45051</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>45051</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45061</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45061</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45062</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45062</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>45063</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45070</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45075</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>45075</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45084</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45084</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>45085</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45086</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45089</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45091</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45091</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45092</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45092</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45096</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45097</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45097</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45098</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45098</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>45099</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45104</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45104</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>45107</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45107</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45109</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>45109</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45110</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45110</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45114</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45117</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45118</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>45126</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>45128</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>45131</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>45132</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>45132</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45145</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45145</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>45149</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>45153</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45153</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>45154</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>45155</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>45155</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45159</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45159</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>45162</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>45162</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>45163</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45163</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>45166</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>45167</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>45167</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>45168</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>45168</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>45169</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45169</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45170</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>45170</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>45173</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45176</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45176</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>45181</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45182</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45182</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>45186</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45190</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>45190</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45194</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45194</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45198</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45199</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45199</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45203</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45204</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45204</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45205</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45205</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45211</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45211</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45212</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45218</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45222</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45222</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45223</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45225</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45225</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45226</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45229</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45229</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45230</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45233</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45236</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45238</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45238</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45243</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45244</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45245</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45245</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45246</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45250</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45251</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45252</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45257</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45258</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45259</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45260</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45265</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45267</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45268</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45271</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45272</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45274</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45278</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45279</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>45281</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45287</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45288</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45293</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45295</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45299</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45300</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45301</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>45307</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45309</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45310</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>45314</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         <v>45315</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50369,14 +50369,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 3126-2024</t>
+          <t>A 3037-2024</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50388,8 +50388,13 @@
           <t>HYLTE</t>
         </is>
       </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G866" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -50433,7 +50438,7 @@
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50488,14 +50493,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 3037-2024</t>
+          <t>A 3126-2024</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50507,13 +50512,8 @@
           <t>HYLTE</t>
         </is>
       </c>
-      <c r="F868" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G868" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -50557,7 +50557,7 @@
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50607,14 +50607,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 4523-2024</t>
+          <t>A 4528-2024</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -50664,14 +50664,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 4527-2024</t>
+          <t>A 4523-2024</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -50721,14 +50721,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 4528-2024</t>
+          <t>A 4527-2024</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -50785,7 +50785,7 @@
         <v>45328</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>45329</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>45330</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45331</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45334</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z881"/>
+  <dimension ref="A1:Z884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44340</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44341</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44347</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44347</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44356</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44356</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44357</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44357</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44363</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44365</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44371</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44373</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44376</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44378</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44384</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44384</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44389</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44396</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44405</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44421</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44427</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44442</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44446</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44448</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44449</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44454</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44454</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44455</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44455</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44456</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44460</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44460</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44475</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44475</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44476</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44476</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44477</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44477</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44480</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44481</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>44481</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44483</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44487</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44487</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44488</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44488</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44489</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44489</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44494</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44495</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44498</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44500</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44501</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44502</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44505</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44508</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44510</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44515</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44523</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44532</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44539</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44559</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44573</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44573</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44575</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44578</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44596</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44600</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44601</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44607</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44613</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44615</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44621</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44624</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44624</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>44631</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44634</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44635</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44637</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44638</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44641</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44648</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44651</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44651</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44655</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44659</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44659</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44671</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44671</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44692</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44693</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44697</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44701</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44701</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44705</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44705</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44711</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44711</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44712</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44712</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44714</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44714</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44726</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44727</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44728</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44735</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44735</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44739</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44739</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44753</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44756</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44756</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44757</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44762</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44763</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44770</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44777</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44795</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>44796</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44796</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44797</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44801</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>44812</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44813</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44818</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44823</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44823</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44830</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44830</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44834</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44834</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44847</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44851</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44865</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44865</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44866</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44867</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44872</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44872</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44873</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44876</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44887</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44893</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44893</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44896</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44896</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44899</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44900</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44900</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44901</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44903</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44907</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44914</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44917</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>44926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44931</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>44950</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>44951</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44953</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44958</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44958</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44964</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44965</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44967</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44970</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44974</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44974</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44981</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44990</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44995</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44995</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44999</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44999</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45002</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45002</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45013</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45014</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45019</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45019</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45020</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45027</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45027</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45028</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45030</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45030</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45035</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45035</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45040</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45042</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45044</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45051</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45051</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45058</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45061</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45061</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45062</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45062</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45063</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45070</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45070</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45075</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45084</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45084</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45085</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45089</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45091</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45091</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45092</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45092</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45096</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45097</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45098</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45098</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45104</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45104</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45109</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45109</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45110</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45110</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45117</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45118</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45126</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45128</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45131</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45132</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45132</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45149</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45153</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45154</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45155</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45155</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45159</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45162</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45163</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45163</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45166</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45167</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45167</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45168</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45168</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45169</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45169</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45170</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45176</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45181</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45182</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45182</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45186</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45190</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45190</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45194</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45194</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45198</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45199</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45199</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45203</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45204</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45204</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45205</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45205</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45211</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45211</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45218</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
         <v>45223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45225</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45226</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45225</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>45229</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45230</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45233</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45236</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45238</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45238</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45243</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45244</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>45245</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45250</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45251</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45252</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45254</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45258</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45260</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45267</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45268</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45271</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45272</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45274</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45278</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45279</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45281</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45287</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45288</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45293</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45295</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45299</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45300</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45301</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45307</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45309</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45310</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50311,14 +50311,14 @@
     <row r="864" ht="15" customHeight="1">
       <c r="A864" t="inlineStr">
         <is>
-          <t>A 2743-2024</t>
+          <t>A 2803-2024</t>
         </is>
       </c>
       <c r="B864" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         </is>
       </c>
       <c r="G864" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -50368,14 +50368,14 @@
     <row r="865" ht="15" customHeight="1">
       <c r="A865" t="inlineStr">
         <is>
-          <t>A 2803-2024</t>
+          <t>A 2743-2024</t>
         </is>
       </c>
       <c r="B865" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -50432,7 +50432,7 @@
         <v>45315</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50482,14 +50482,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 3037-2024</t>
+          <t>A 3132-2024</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50501,13 +50501,8 @@
           <t>HYLTE</t>
         </is>
       </c>
-      <c r="F867" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G867" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -50544,14 +50539,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 3122-2024</t>
+          <t>A 3037-2024</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50569,7 +50564,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -50606,14 +50601,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 3126-2024</t>
+          <t>A 3122-2024</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50625,8 +50620,13 @@
           <t>HYLTE</t>
         </is>
       </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G869" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -50663,14 +50663,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 3132-2024</t>
+          <t>A 3126-2024</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -50727,7 +50727,7 @@
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45327</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45328</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45329</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45330</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45334</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51181,14 +51181,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 6793-2024</t>
+          <t>A 6779-2024</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 6779-2024</t>
+          <t>A 6787-2024</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -51302,67 +51302,238 @@
       </c>
       <c r="R880" s="2" t="inlineStr"/>
     </row>
-    <row r="881">
+    <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 6787-2024</t>
+          <t>A 6793-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C881" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G881" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H881" t="n">
+        <v>0</v>
+      </c>
+      <c r="I881" t="n">
+        <v>0</v>
+      </c>
+      <c r="J881" t="n">
+        <v>0</v>
+      </c>
+      <c r="K881" t="n">
+        <v>0</v>
+      </c>
+      <c r="L881" t="n">
+        <v>0</v>
+      </c>
+      <c r="M881" t="n">
+        <v>0</v>
+      </c>
+      <c r="N881" t="n">
+        <v>0</v>
+      </c>
+      <c r="O881" t="n">
+        <v>0</v>
+      </c>
+      <c r="P881" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q881" t="n">
+        <v>0</v>
+      </c>
+      <c r="R881" s="2" t="inlineStr"/>
+    </row>
+    <row r="882" ht="15" customHeight="1">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>A 7097-2024</t>
+        </is>
+      </c>
+      <c r="B882" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C882" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G882" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H882" t="n">
+        <v>0</v>
+      </c>
+      <c r="I882" t="n">
+        <v>0</v>
+      </c>
+      <c r="J882" t="n">
+        <v>0</v>
+      </c>
+      <c r="K882" t="n">
+        <v>0</v>
+      </c>
+      <c r="L882" t="n">
+        <v>0</v>
+      </c>
+      <c r="M882" t="n">
+        <v>0</v>
+      </c>
+      <c r="N882" t="n">
+        <v>0</v>
+      </c>
+      <c r="O882" t="n">
+        <v>0</v>
+      </c>
+      <c r="P882" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q882" t="n">
+        <v>0</v>
+      </c>
+      <c r="R882" s="2" t="inlineStr"/>
+    </row>
+    <row r="883" ht="15" customHeight="1">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>A 7244-2024</t>
+        </is>
+      </c>
+      <c r="B883" s="1" t="n">
         <v>45344</v>
       </c>
-      <c r="D881" t="inlineStr">
-        <is>
-          <t>HALLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E881" t="inlineStr">
-        <is>
-          <t>HYLTE</t>
-        </is>
-      </c>
-      <c r="F881" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="G881" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H881" t="n">
-        <v>0</v>
-      </c>
-      <c r="I881" t="n">
-        <v>0</v>
-      </c>
-      <c r="J881" t="n">
-        <v>0</v>
-      </c>
-      <c r="K881" t="n">
-        <v>0</v>
-      </c>
-      <c r="L881" t="n">
-        <v>0</v>
-      </c>
-      <c r="M881" t="n">
-        <v>0</v>
-      </c>
-      <c r="N881" t="n">
-        <v>0</v>
-      </c>
-      <c r="O881" t="n">
-        <v>0</v>
-      </c>
-      <c r="P881" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q881" t="n">
-        <v>0</v>
-      </c>
-      <c r="R881" s="2" t="inlineStr"/>
+      <c r="C883" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G883" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H883" t="n">
+        <v>0</v>
+      </c>
+      <c r="I883" t="n">
+        <v>0</v>
+      </c>
+      <c r="J883" t="n">
+        <v>0</v>
+      </c>
+      <c r="K883" t="n">
+        <v>0</v>
+      </c>
+      <c r="L883" t="n">
+        <v>0</v>
+      </c>
+      <c r="M883" t="n">
+        <v>0</v>
+      </c>
+      <c r="N883" t="n">
+        <v>0</v>
+      </c>
+      <c r="O883" t="n">
+        <v>0</v>
+      </c>
+      <c r="P883" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q883" t="n">
+        <v>0</v>
+      </c>
+      <c r="R883" s="2" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>A 7248-2024</t>
+        </is>
+      </c>
+      <c r="B884" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C884" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G884" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H884" t="n">
+        <v>0</v>
+      </c>
+      <c r="I884" t="n">
+        <v>0</v>
+      </c>
+      <c r="J884" t="n">
+        <v>0</v>
+      </c>
+      <c r="K884" t="n">
+        <v>0</v>
+      </c>
+      <c r="L884" t="n">
+        <v>0</v>
+      </c>
+      <c r="M884" t="n">
+        <v>0</v>
+      </c>
+      <c r="N884" t="n">
+        <v>0</v>
+      </c>
+      <c r="O884" t="n">
+        <v>0</v>
+      </c>
+      <c r="P884" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q884" t="n">
+        <v>0</v>
+      </c>
+      <c r="R884" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44340</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44341</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44347</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44347</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44356</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44356</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44357</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44357</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44363</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44365</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44371</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44373</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44376</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44378</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44384</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44384</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44389</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44396</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44405</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44421</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44427</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44442</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44446</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44448</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44449</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44454</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44454</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44455</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44455</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44456</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44460</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44460</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44475</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44475</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44476</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44476</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44477</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44477</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44480</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44481</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>44481</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44483</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44487</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44487</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44488</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44488</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44489</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44489</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44494</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44495</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44498</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44500</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44501</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44502</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44505</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44508</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44510</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44515</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44523</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44532</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44539</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44559</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44573</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44573</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44575</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44578</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44596</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44600</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44601</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44607</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44613</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44615</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44621</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44624</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44624</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>44631</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44634</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44635</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44637</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44638</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44641</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44648</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44651</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44651</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44655</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44659</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44659</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44671</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44671</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44692</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44693</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44697</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44701</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44701</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44705</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44705</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44711</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44711</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44712</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44712</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44714</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44714</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44726</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44727</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44728</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44735</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44735</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44739</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44739</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44753</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44756</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44756</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44757</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44762</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44763</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44770</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44777</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44795</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>44796</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44796</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44797</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44801</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>44812</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44813</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44818</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44823</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44823</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44830</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44830</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44834</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44834</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44847</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44851</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44865</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44865</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44866</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44867</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44872</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44872</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44873</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44876</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44887</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44893</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44893</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44896</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44896</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44899</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44900</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44900</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44901</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44903</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44907</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44914</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44917</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>44926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44931</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>44950</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>44951</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44953</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44958</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44958</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44964</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44965</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44967</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44970</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44974</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44974</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44981</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44990</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44995</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44995</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44999</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44999</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45002</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45002</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45013</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45014</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45019</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45019</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45020</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45027</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45027</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45028</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45030</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45030</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45035</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45035</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45040</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45042</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45044</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45051</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45051</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45058</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45061</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45061</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45062</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45062</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45063</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45070</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45070</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45075</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45084</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45084</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45085</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45089</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45091</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45091</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45092</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45092</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45096</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45097</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45098</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45098</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45104</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45104</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45109</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45109</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45110</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45110</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45117</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45118</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45126</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45128</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45131</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45132</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45132</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45149</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45153</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45154</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45155</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45155</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45159</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45162</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45163</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45163</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45166</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45167</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45167</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45168</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45168</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45169</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45169</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45170</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45176</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45181</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45182</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45182</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45186</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45190</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45190</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45194</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45194</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45198</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45199</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45199</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45203</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45204</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45204</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45205</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45205</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45211</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45211</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45218</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
         <v>45223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45225</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45226</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45225</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>45229</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45230</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45233</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45236</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45238</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45238</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45243</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45244</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>45245</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45250</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45251</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45252</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45254</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45258</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45260</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45267</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45268</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45271</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45272</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45274</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45278</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45279</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45281</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45287</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45288</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45293</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45295</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45299</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45300</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45301</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45307</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45309</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45310</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45314</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45315</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50482,14 +50482,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 3132-2024</t>
+          <t>A 3037-2024</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50501,8 +50501,13 @@
           <t>HYLTE</t>
         </is>
       </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G867" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -50539,14 +50544,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 3037-2024</t>
+          <t>A 3122-2024</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50564,7 +50569,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -50601,14 +50606,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 3122-2024</t>
+          <t>A 3126-2024</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50620,13 +50625,8 @@
           <t>HYLTE</t>
         </is>
       </c>
-      <c r="F869" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G869" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -50663,14 +50663,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 3126-2024</t>
+          <t>A 3132-2024</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -50727,7 +50727,7 @@
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45327</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45328</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45329</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45330</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45334</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51181,14 +51181,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 6779-2024</t>
+          <t>A 6793-2024</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 6787-2024</t>
+          <t>A 6779-2024</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -51305,14 +51305,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 6793-2024</t>
+          <t>A 6787-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -51374,7 +51374,7 @@
         <v>45343</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45344</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45344</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44340</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44341</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44347</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44347</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44356</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44356</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44357</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44357</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44363</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44365</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44371</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44373</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44376</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44378</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44384</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44384</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44389</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44396</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44405</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44421</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44427</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44442</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44446</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44448</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44449</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44454</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44454</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44455</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44455</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44456</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44460</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44460</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44475</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44475</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44476</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44476</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44477</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44477</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44480</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44481</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>44481</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44483</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44487</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44487</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44488</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44488</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44489</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44489</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44494</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44495</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44498</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44500</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44501</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44502</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44505</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44508</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44510</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44515</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44523</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44532</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44539</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44559</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44573</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44573</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44575</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44578</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44596</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44600</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44601</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44607</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44613</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44615</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44621</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44624</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44624</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>44631</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44634</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44635</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44637</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44638</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44641</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44648</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44651</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44651</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44655</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44659</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44659</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44671</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44671</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44692</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44693</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44697</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44701</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44701</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44705</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44705</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44711</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44711</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44712</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44712</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44714</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44714</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44726</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44727</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44728</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44735</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44735</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44739</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44739</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44753</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44756</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44756</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44757</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44762</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44763</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44770</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44777</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44795</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>44796</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44796</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44797</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44801</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>44812</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44813</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44818</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44823</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44823</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44830</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44830</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44834</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44834</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44847</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44851</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44865</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44865</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44866</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44867</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44872</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44872</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44873</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44876</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44887</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44893</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44893</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44896</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44896</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44899</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44900</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44900</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44901</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44903</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44907</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44914</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44917</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>44926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44931</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>44950</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>44951</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44953</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44958</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44958</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44964</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44965</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44967</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44970</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44974</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44974</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44981</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44990</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44995</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44995</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44999</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44999</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45002</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45002</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45013</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45014</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45019</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45019</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45020</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45027</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45027</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45028</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45030</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45030</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45035</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45035</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45040</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45042</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45044</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45051</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45051</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45058</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45061</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45061</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45062</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45062</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45063</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45070</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45070</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45075</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45084</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45084</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45085</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45089</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45091</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45091</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45092</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45092</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45096</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45097</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45098</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45098</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45104</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45104</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45109</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45109</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45110</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45110</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45117</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45118</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45126</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45128</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45131</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45132</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45132</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45149</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45153</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45154</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45155</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45155</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45159</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45162</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45163</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45163</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45166</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45167</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45167</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45168</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45168</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45169</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45169</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45170</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45176</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45181</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45182</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45182</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45186</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45190</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45190</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45194</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45194</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45198</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45199</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45199</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45203</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45204</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45204</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45205</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45205</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45211</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45211</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45218</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
         <v>45223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45225</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45226</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45225</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>45229</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45230</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45233</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45236</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45238</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45238</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45243</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45244</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>45245</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45250</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45251</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45252</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45254</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45258</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45260</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45267</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45268</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45271</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45272</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45274</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45278</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45279</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45281</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45287</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45288</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45293</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45295</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45299</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45300</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45301</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45307</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45309</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45310</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45314</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45315</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45316</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45327</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45328</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45329</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45330</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45334</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51181,14 +51181,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 6793-2024</t>
+          <t>A 6779-2024</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 6779-2024</t>
+          <t>A 6787-2024</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -51305,14 +51305,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 6787-2024</t>
+          <t>A 6793-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -51374,7 +51374,7 @@
         <v>45343</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45344</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45344</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44340</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44341</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44347</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44347</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44356</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44356</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44357</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44357</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44363</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44365</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44371</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44373</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44376</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44378</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44384</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44384</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44389</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44396</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44405</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44421</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44427</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44442</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44446</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44448</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44449</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44454</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44454</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44455</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44455</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44456</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44460</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44460</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44475</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44475</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44476</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44476</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44477</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44477</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44480</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44481</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>44481</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44483</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44487</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44487</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44488</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44488</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44489</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44489</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44494</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44495</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44498</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44500</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44501</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44502</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44505</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44508</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44510</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44515</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44523</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44532</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44539</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44559</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44573</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44573</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44575</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44578</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44596</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44600</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44601</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44607</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44613</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44615</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44621</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44624</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44624</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>44631</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44634</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44635</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44637</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44638</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44641</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44648</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44651</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44651</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44655</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44659</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44659</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44671</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44671</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44692</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44693</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44697</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44701</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44701</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44705</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44705</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44711</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44711</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44712</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44712</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44714</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44714</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44726</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44727</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44728</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44735</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44735</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44739</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44739</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44753</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44756</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44756</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44757</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44762</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44763</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44770</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44777</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44795</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>44796</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44796</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44797</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44801</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>44812</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44813</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44818</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44823</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44823</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44830</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44830</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44834</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44834</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44847</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44851</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44865</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44865</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44866</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44867</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44872</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44872</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44873</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44876</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44887</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44893</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44893</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44896</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44896</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44899</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44900</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44900</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44901</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44903</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44907</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44914</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44917</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>44926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44931</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>44950</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>44951</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44953</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44958</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44958</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44964</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44965</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44967</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44970</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44974</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44974</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44981</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44990</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44995</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44995</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44999</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44999</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45002</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45002</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45013</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45014</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45019</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45019</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45020</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45027</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45027</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45028</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45030</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45030</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45035</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45035</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45040</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45042</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45044</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45051</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45051</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45058</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45061</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45061</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45062</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45062</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45063</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45070</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45070</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45075</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45084</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45084</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45085</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45089</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45091</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45091</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45092</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45092</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45096</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45097</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45098</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45098</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45104</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45104</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45109</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45109</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45110</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45110</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45117</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45118</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45126</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45128</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45131</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45132</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45132</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45149</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45153</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45154</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45155</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45155</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45159</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45162</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45163</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45163</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45166</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45167</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45167</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45168</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45168</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45169</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45169</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45170</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45176</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45181</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45182</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45182</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45186</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45190</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45190</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45194</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45194</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45198</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45199</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45199</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45203</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45204</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45204</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45205</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45205</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45211</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45211</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45218</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
         <v>45223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45225</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45226</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45225</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>45229</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45230</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45233</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45236</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45238</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45238</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45243</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45244</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>45245</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45250</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45251</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45252</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45254</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45258</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45260</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45267</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45268</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45271</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45272</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45274</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45278</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45279</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45281</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45287</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45288</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45293</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45295</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45299</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45300</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45301</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45307</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45309</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45310</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45314</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45315</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45316</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50720,14 +50720,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 4528-2024</t>
+          <t>A 4523-2024</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -50777,14 +50777,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 4523-2024</t>
+          <t>A 4527-2024</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -50834,14 +50834,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 4527-2024</t>
+          <t>A 4528-2024</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -50898,7 +50898,7 @@
         <v>45328</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45329</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45330</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45334</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51181,14 +51181,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 6779-2024</t>
+          <t>A 6793-2024</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 6787-2024</t>
+          <t>A 6779-2024</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -51305,14 +51305,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 6793-2024</t>
+          <t>A 6787-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -51374,7 +51374,7 @@
         <v>45343</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51424,14 +51424,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 7244-2024</t>
+          <t>A 7248-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -51481,14 +51481,14 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 7248-2024</t>
+          <t>A 7244-2024</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z884"/>
+  <dimension ref="A1:Z886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44340</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44341</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44347</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44347</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44356</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44356</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44357</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44357</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44363</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44365</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44371</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44373</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44376</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44378</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44384</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44384</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44389</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44396</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44405</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44421</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44427</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44442</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44446</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44448</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44449</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44454</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44454</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44455</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44455</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44456</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44460</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44460</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44475</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44475</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44476</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44476</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44477</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44477</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44480</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44481</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>44481</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44483</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44487</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44487</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44488</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44488</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44489</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44489</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44494</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44495</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44498</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44500</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44501</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44502</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44505</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44508</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44510</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44515</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44523</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44532</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44539</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44559</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44573</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44573</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44575</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44578</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44596</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44600</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44601</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44607</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44613</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44615</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44621</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44624</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44624</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>44631</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44634</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44635</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44637</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44638</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44641</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44648</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44651</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44651</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44655</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44659</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44659</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44671</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44671</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44692</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44693</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44697</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44701</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44701</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44705</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44705</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44711</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44711</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44712</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44712</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44714</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44714</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44726</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44727</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44728</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44735</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44735</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44739</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44739</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44753</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44756</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44756</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44757</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44762</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44763</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44770</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44777</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44795</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>44796</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44796</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44797</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44801</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>44812</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44813</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44818</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44823</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44823</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44830</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44830</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44834</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44834</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44847</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44851</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44865</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44865</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44866</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44867</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44872</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44872</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44873</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44876</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44887</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44893</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44893</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44896</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44896</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44899</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44900</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44900</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44901</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44903</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44907</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44914</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44917</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>44926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44931</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>44950</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>44951</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44953</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44958</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44958</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44964</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44965</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44967</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44970</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44974</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44974</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44981</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44990</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44995</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44995</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44999</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44999</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45002</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45002</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45013</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45014</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45019</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45019</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45020</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45027</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45027</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45028</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45030</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45030</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45035</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45035</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45040</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45042</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45044</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45051</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45051</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45058</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45061</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45061</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45062</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45062</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45063</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45070</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45070</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45075</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45084</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45084</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45085</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45089</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45091</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45091</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45092</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45092</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45096</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45097</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45098</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45098</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45104</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45104</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45109</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45109</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45110</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45110</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45117</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45118</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45126</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45128</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45131</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45132</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45132</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45149</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45153</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45154</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45155</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45155</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45159</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45162</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45163</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45163</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45166</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45167</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45167</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45168</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45168</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45169</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45169</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45170</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45176</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45181</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45182</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45182</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45186</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45190</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45190</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45194</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45194</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45198</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45199</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45199</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45203</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45204</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45204</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45205</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45205</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45211</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45211</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45218</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
         <v>45223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45225</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45226</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45225</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>45229</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45230</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45233</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45236</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45238</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45238</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45243</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45244</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>45245</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45250</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45251</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45252</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45254</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45258</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45260</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45267</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45268</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45271</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45272</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45274</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45278</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45279</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45281</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45287</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45288</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45293</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45295</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45299</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45300</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45301</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45307</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45309</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45310</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45314</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45315</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45316</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50720,14 +50720,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 4523-2024</t>
+          <t>A 4528-2024</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -50777,14 +50777,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 4527-2024</t>
+          <t>A 4523-2024</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -50834,14 +50834,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 4528-2024</t>
+          <t>A 4527-2024</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -50898,7 +50898,7 @@
         <v>45328</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45329</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45330</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45334</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51181,14 +51181,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 6793-2024</t>
+          <t>A 6779-2024</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 6779-2024</t>
+          <t>A 6793-2024</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -51312,7 +51312,7 @@
         <v>45342</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45343</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51424,14 +51424,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 7248-2024</t>
+          <t>A 7244-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -51478,62 +51478,181 @@
       </c>
       <c r="R883" s="2" t="inlineStr"/>
     </row>
-    <row r="884">
+    <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 7244-2024</t>
+          <t>A 7248-2024</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C884" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G884" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H884" t="n">
+        <v>0</v>
+      </c>
+      <c r="I884" t="n">
+        <v>0</v>
+      </c>
+      <c r="J884" t="n">
+        <v>0</v>
+      </c>
+      <c r="K884" t="n">
+        <v>0</v>
+      </c>
+      <c r="L884" t="n">
+        <v>0</v>
+      </c>
+      <c r="M884" t="n">
+        <v>0</v>
+      </c>
+      <c r="N884" t="n">
+        <v>0</v>
+      </c>
+      <c r="O884" t="n">
+        <v>0</v>
+      </c>
+      <c r="P884" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q884" t="n">
+        <v>0</v>
+      </c>
+      <c r="R884" s="2" t="inlineStr"/>
+    </row>
+    <row r="885" ht="15" customHeight="1">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>A 7588-2024</t>
+        </is>
+      </c>
+      <c r="B885" s="1" t="n">
         <v>45348</v>
       </c>
-      <c r="D884" t="inlineStr">
-        <is>
-          <t>HALLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E884" t="inlineStr">
-        <is>
-          <t>HYLTE</t>
-        </is>
-      </c>
-      <c r="G884" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H884" t="n">
-        <v>0</v>
-      </c>
-      <c r="I884" t="n">
-        <v>0</v>
-      </c>
-      <c r="J884" t="n">
-        <v>0</v>
-      </c>
-      <c r="K884" t="n">
-        <v>0</v>
-      </c>
-      <c r="L884" t="n">
-        <v>0</v>
-      </c>
-      <c r="M884" t="n">
-        <v>0</v>
-      </c>
-      <c r="N884" t="n">
-        <v>0</v>
-      </c>
-      <c r="O884" t="n">
-        <v>0</v>
-      </c>
-      <c r="P884" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q884" t="n">
-        <v>0</v>
-      </c>
-      <c r="R884" s="2" t="inlineStr"/>
+      <c r="C885" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G885" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H885" t="n">
+        <v>0</v>
+      </c>
+      <c r="I885" t="n">
+        <v>0</v>
+      </c>
+      <c r="J885" t="n">
+        <v>0</v>
+      </c>
+      <c r="K885" t="n">
+        <v>0</v>
+      </c>
+      <c r="L885" t="n">
+        <v>0</v>
+      </c>
+      <c r="M885" t="n">
+        <v>0</v>
+      </c>
+      <c r="N885" t="n">
+        <v>0</v>
+      </c>
+      <c r="O885" t="n">
+        <v>0</v>
+      </c>
+      <c r="P885" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q885" t="n">
+        <v>0</v>
+      </c>
+      <c r="R885" s="2" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>A 7679-2024</t>
+        </is>
+      </c>
+      <c r="B886" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C886" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G886" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H886" t="n">
+        <v>0</v>
+      </c>
+      <c r="I886" t="n">
+        <v>0</v>
+      </c>
+      <c r="J886" t="n">
+        <v>0</v>
+      </c>
+      <c r="K886" t="n">
+        <v>0</v>
+      </c>
+      <c r="L886" t="n">
+        <v>0</v>
+      </c>
+      <c r="M886" t="n">
+        <v>0</v>
+      </c>
+      <c r="N886" t="n">
+        <v>0</v>
+      </c>
+      <c r="O886" t="n">
+        <v>0</v>
+      </c>
+      <c r="P886" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q886" t="n">
+        <v>0</v>
+      </c>
+      <c r="R886" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44340</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44341</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44347</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44347</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44356</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44356</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44357</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44357</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44363</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44365</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44371</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44373</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44376</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44378</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44384</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44384</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44389</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44396</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44405</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44421</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44427</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44442</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44446</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44448</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44449</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44454</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44454</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44455</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44455</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44456</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44460</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44460</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44475</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44475</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44476</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44476</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44477</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44477</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44480</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44481</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>44481</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44483</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44487</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44487</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44488</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44488</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44489</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44489</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44494</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44495</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44498</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44500</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44501</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44502</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44505</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44508</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44510</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44515</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44523</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44532</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44539</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44559</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44573</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44573</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44575</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44578</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44596</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44600</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44601</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44607</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44613</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44615</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44621</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44624</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44624</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>44631</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44634</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44635</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44637</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44638</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44641</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44648</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44651</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44651</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44655</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44659</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44659</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44671</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44671</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44692</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44693</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44697</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44701</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44701</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44705</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44705</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44711</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44711</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44712</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44712</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44714</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44714</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44726</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44727</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44728</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44735</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44735</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44739</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44739</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44753</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44756</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44756</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44757</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44762</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44763</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44770</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44777</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44795</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>44796</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44796</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44797</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44801</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>44812</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44813</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44818</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44823</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44823</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44830</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44830</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44834</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44834</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44847</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44851</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44865</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44865</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44866</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44867</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44872</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44872</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44873</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44876</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44887</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44893</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44893</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44896</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44896</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44899</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44900</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44900</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44901</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44903</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44907</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44914</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44917</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>44926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44931</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>44950</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>44951</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44953</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44958</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44958</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44964</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44965</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44967</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44970</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44974</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44974</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44981</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44990</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44995</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44995</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44999</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44999</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45002</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45002</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45013</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45014</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45019</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45019</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45020</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45027</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45027</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45028</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45030</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45030</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45035</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45035</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45040</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45042</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45044</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45051</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45051</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45058</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45061</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45061</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45062</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45062</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45063</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45070</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45070</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45075</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45084</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45084</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45085</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45089</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45091</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45091</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45092</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45092</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45096</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45097</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45098</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45098</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45104</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45104</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45109</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45109</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45110</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45110</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45117</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45118</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45126</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45128</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45131</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45132</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45132</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45149</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45153</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45154</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45155</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45155</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45159</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45162</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45163</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45163</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45166</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45167</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45167</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45168</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45168</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45169</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45169</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45170</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45176</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45181</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45182</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45182</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45186</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45190</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45190</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45194</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45194</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45198</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45199</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45199</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45203</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45204</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45204</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45205</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45205</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45211</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45211</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45218</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
         <v>45223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45225</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45226</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45225</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>45229</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45230</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45233</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45236</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45238</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45238</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45243</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45244</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>45245</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45250</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45251</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45252</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45254</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45258</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45260</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45267</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45268</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45271</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45272</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45274</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45278</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45279</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45281</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45287</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45288</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45293</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45295</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45299</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45300</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45301</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45307</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45309</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45310</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45314</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45315</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45316</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50720,14 +50720,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 4528-2024</t>
+          <t>A 4523-2024</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -50777,14 +50777,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 4523-2024</t>
+          <t>A 4527-2024</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -50834,14 +50834,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 4527-2024</t>
+          <t>A 4528-2024</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -50898,7 +50898,7 @@
         <v>45328</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45329</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45330</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45334</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51243,14 +51243,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 6793-2024</t>
+          <t>A 6787-2024</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -51305,14 +51305,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 6787-2024</t>
+          <t>A 6793-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -51374,7 +51374,7 @@
         <v>45343</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45344</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45344</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45348</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45348</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z886"/>
+  <dimension ref="A1:Z887"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44340</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44341</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44347</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44347</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44356</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44356</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44357</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44357</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44363</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44365</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44371</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44373</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44376</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44378</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44384</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44384</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44389</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44396</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44405</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44421</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44427</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44442</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44446</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44448</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44449</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44454</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44454</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44455</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44455</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44456</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44460</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44460</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44475</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44475</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44476</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44476</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44477</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44477</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44480</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44481</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>44481</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44483</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44487</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44487</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44488</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44488</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44489</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44489</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44494</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44495</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44498</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44500</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44501</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44502</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44505</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44508</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44510</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44515</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44523</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44532</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44539</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44559</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44573</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44573</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44575</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44578</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44596</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44600</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44601</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44607</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44613</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44615</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44621</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44624</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44624</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>44631</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44634</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44635</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44637</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44638</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44641</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44648</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44651</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44651</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44655</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44659</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44659</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44671</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44671</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44692</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44693</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44697</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44701</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44701</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44705</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44705</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44711</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44711</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44712</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44712</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44714</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44714</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44726</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44727</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44728</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44735</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44735</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44739</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44739</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44753</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44756</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44756</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44757</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44762</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44763</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44770</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44777</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44795</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>44796</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44796</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44797</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44801</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>44812</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44813</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44818</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44823</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44823</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44830</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44830</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44834</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44834</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44847</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44851</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44865</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44865</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44866</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44867</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44872</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44872</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44873</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44876</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44887</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44893</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44893</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44896</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44896</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44899</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44900</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44900</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44901</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44903</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44907</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44914</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44917</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>44926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44931</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>44950</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>44951</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44953</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44958</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44958</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44964</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44965</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44967</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44970</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44974</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44974</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44981</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44990</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44995</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44995</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44999</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44999</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45002</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45002</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45013</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45014</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45019</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45019</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45020</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45027</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45027</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45028</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45030</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45030</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45035</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45035</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45040</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45042</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45044</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45051</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45051</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45058</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45061</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45061</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45062</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45062</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45063</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45070</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45070</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45075</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45084</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45084</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45085</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45089</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45091</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45091</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45092</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45092</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45096</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45097</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45098</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45098</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45104</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45104</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45109</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45109</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45110</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45110</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45117</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45118</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45126</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45128</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45131</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45132</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45132</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45149</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45153</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45154</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45155</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45155</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45159</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45162</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45163</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45163</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45166</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45167</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45167</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45168</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45168</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45169</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45169</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45170</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45176</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45181</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45182</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45182</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45186</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45190</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45190</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45194</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45194</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45198</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45199</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45199</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45203</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45204</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45204</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45205</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45205</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45211</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45211</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45218</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
         <v>45223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45225</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45226</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45225</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>45229</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45230</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45233</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45236</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45238</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45238</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45243</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45244</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>45245</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45250</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45251</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45252</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45254</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45258</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45260</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45267</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45268</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45271</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45272</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45274</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45278</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45279</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45281</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45287</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45288</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45293</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45295</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45299</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45300</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45301</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45307</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45309</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45310</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45314</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45315</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45316</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45327</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45328</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45329</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45330</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45334</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>45342</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45343</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45344</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45344</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45348</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
       </c>
       <c r="R885" s="2" t="inlineStr"/>
     </row>
-    <row r="886">
+    <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
           <t>A 7679-2024</t>
@@ -51607,7 +51607,7 @@
         <v>45348</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51653,6 +51653,63 @@
         <v>0</v>
       </c>
       <c r="R886" s="2" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>A 7934-2024</t>
+        </is>
+      </c>
+      <c r="B887" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C887" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G887" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H887" t="n">
+        <v>0</v>
+      </c>
+      <c r="I887" t="n">
+        <v>0</v>
+      </c>
+      <c r="J887" t="n">
+        <v>0</v>
+      </c>
+      <c r="K887" t="n">
+        <v>0</v>
+      </c>
+      <c r="L887" t="n">
+        <v>0</v>
+      </c>
+      <c r="M887" t="n">
+        <v>0</v>
+      </c>
+      <c r="N887" t="n">
+        <v>0</v>
+      </c>
+      <c r="O887" t="n">
+        <v>0</v>
+      </c>
+      <c r="P887" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q887" t="n">
+        <v>0</v>
+      </c>
+      <c r="R887" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z887"/>
+  <dimension ref="A1:Z891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44340</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44341</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44347</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44347</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44356</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44356</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44357</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44357</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44363</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44365</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44371</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44373</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44376</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44378</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44384</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44384</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44389</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44396</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44405</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44421</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44427</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44442</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44446</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44448</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44449</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44454</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44454</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44455</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44455</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44456</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44460</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44460</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44475</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44475</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44476</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44476</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44477</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44477</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44480</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44481</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>44481</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44483</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44487</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44487</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44488</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44488</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44489</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44489</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44494</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44495</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44498</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44500</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44501</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44502</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44505</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44508</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44510</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44515</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44523</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44532</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44539</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44559</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44573</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44573</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44575</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44578</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44596</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44600</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44601</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44607</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44613</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44615</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44621</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44624</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44624</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>44631</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44634</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44635</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44637</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44638</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44641</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44648</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44651</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44651</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44655</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44659</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44659</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44671</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44671</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44692</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44693</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44697</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44701</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44701</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44705</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44705</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44711</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44711</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44712</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44712</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44714</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44714</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44726</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44727</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44728</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44735</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44735</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44739</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44739</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44753</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44756</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44756</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44757</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44762</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44763</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44770</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44777</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44795</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>44796</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44796</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44797</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44801</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>44812</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44813</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44818</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44823</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44823</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44830</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44830</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44834</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44834</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44847</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44851</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44865</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44865</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44866</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44867</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44872</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44872</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44873</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44876</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44887</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44893</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44893</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44896</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44896</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44899</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44900</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44900</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44901</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44903</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44907</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44914</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44917</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>44926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44931</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>44950</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>44951</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44953</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44958</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44958</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44964</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44965</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44967</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44970</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44974</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44974</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44981</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44990</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44995</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44995</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44999</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44999</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45002</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45002</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45013</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45014</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45019</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45019</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45020</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45027</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45027</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45028</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45030</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45030</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45035</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45035</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45040</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45042</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45044</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45051</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45051</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45058</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45061</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45061</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45062</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45062</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45063</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45070</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45070</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45075</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45084</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45084</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45085</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45089</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45091</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45091</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45092</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45092</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45096</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45097</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45098</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45098</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45104</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45104</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45109</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45109</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45110</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45110</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45117</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45118</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45126</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45128</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45131</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45132</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45132</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45149</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45153</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45154</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45155</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45155</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45159</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45162</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45163</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45163</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45166</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45167</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45167</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45168</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45168</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45169</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45169</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45170</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45176</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45181</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45182</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45182</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45186</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45190</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45190</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45194</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45194</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45198</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45199</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45199</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45203</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45204</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45204</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45205</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45205</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45211</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45211</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45218</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
         <v>45223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45225</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45226</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45225</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>45229</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45230</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45233</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45236</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45238</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45238</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45243</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45244</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>45245</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45250</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45251</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45252</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45254</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45258</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45260</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45267</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45268</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45271</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45272</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45274</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45278</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45279</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45281</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45287</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45288</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45293</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45295</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45299</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45300</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45301</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45307</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45309</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45310</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45314</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45315</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45316</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50720,14 +50720,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 4523-2024</t>
+          <t>A 4528-2024</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -50777,14 +50777,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 4527-2024</t>
+          <t>A 4523-2024</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -50834,14 +50834,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 4528-2024</t>
+          <t>A 4527-2024</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -50898,7 +50898,7 @@
         <v>45328</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45329</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45330</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45334</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51243,14 +51243,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 6787-2024</t>
+          <t>A 6793-2024</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -51305,14 +51305,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 6793-2024</t>
+          <t>A 6787-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -51374,7 +51374,7 @@
         <v>45343</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45344</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45344</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45348</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45348</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51654,7 +51654,7 @@
       </c>
       <c r="R886" s="2" t="inlineStr"/>
     </row>
-    <row r="887">
+    <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
           <t>A 7934-2024</t>
@@ -51664,7 +51664,7 @@
         <v>45350</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51710,6 +51710,234 @@
         <v>0</v>
       </c>
       <c r="R887" s="2" t="inlineStr"/>
+    </row>
+    <row r="888" ht="15" customHeight="1">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>A 8122-2024</t>
+        </is>
+      </c>
+      <c r="B888" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="C888" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G888" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H888" t="n">
+        <v>0</v>
+      </c>
+      <c r="I888" t="n">
+        <v>0</v>
+      </c>
+      <c r="J888" t="n">
+        <v>0</v>
+      </c>
+      <c r="K888" t="n">
+        <v>0</v>
+      </c>
+      <c r="L888" t="n">
+        <v>0</v>
+      </c>
+      <c r="M888" t="n">
+        <v>0</v>
+      </c>
+      <c r="N888" t="n">
+        <v>0</v>
+      </c>
+      <c r="O888" t="n">
+        <v>0</v>
+      </c>
+      <c r="P888" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q888" t="n">
+        <v>0</v>
+      </c>
+      <c r="R888" s="2" t="inlineStr"/>
+    </row>
+    <row r="889" ht="15" customHeight="1">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>A 8140-2024</t>
+        </is>
+      </c>
+      <c r="B889" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="C889" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G889" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H889" t="n">
+        <v>0</v>
+      </c>
+      <c r="I889" t="n">
+        <v>0</v>
+      </c>
+      <c r="J889" t="n">
+        <v>0</v>
+      </c>
+      <c r="K889" t="n">
+        <v>0</v>
+      </c>
+      <c r="L889" t="n">
+        <v>0</v>
+      </c>
+      <c r="M889" t="n">
+        <v>0</v>
+      </c>
+      <c r="N889" t="n">
+        <v>0</v>
+      </c>
+      <c r="O889" t="n">
+        <v>0</v>
+      </c>
+      <c r="P889" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q889" t="n">
+        <v>0</v>
+      </c>
+      <c r="R889" s="2" t="inlineStr"/>
+    </row>
+    <row r="890" ht="15" customHeight="1">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>A 8128-2024</t>
+        </is>
+      </c>
+      <c r="B890" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="C890" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G890" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H890" t="n">
+        <v>0</v>
+      </c>
+      <c r="I890" t="n">
+        <v>0</v>
+      </c>
+      <c r="J890" t="n">
+        <v>0</v>
+      </c>
+      <c r="K890" t="n">
+        <v>0</v>
+      </c>
+      <c r="L890" t="n">
+        <v>0</v>
+      </c>
+      <c r="M890" t="n">
+        <v>0</v>
+      </c>
+      <c r="N890" t="n">
+        <v>0</v>
+      </c>
+      <c r="O890" t="n">
+        <v>0</v>
+      </c>
+      <c r="P890" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q890" t="n">
+        <v>0</v>
+      </c>
+      <c r="R890" s="2" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>A 8135-2024</t>
+        </is>
+      </c>
+      <c r="B891" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="C891" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G891" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H891" t="n">
+        <v>0</v>
+      </c>
+      <c r="I891" t="n">
+        <v>0</v>
+      </c>
+      <c r="J891" t="n">
+        <v>0</v>
+      </c>
+      <c r="K891" t="n">
+        <v>0</v>
+      </c>
+      <c r="L891" t="n">
+        <v>0</v>
+      </c>
+      <c r="M891" t="n">
+        <v>0</v>
+      </c>
+      <c r="N891" t="n">
+        <v>0</v>
+      </c>
+      <c r="O891" t="n">
+        <v>0</v>
+      </c>
+      <c r="P891" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q891" t="n">
+        <v>0</v>
+      </c>
+      <c r="R891" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z891"/>
+  <dimension ref="A1:Z900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44340</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44341</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44347</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44347</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44356</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44356</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44356</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44356</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44356</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44356</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44357</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44357</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44363</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44365</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44371</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44371</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44373</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44375</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44376</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44378</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44384</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44384</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44384</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44389</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44396</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44405</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44421</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44427</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44442</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44446</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44448</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44449</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44454</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44454</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44454</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44455</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44455</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44455</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44456</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44460</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44460</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44469</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44475</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44475</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44476</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44476</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44477</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44477</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44477</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44480</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44481</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>44481</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>44482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44483</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44483</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44483</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44483</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44487</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44487</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44488</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44488</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44489</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44489</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44489</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44494</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44495</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44495</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44498</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44500</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44501</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44502</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44505</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44508</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44510</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44515</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44523</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44529</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44530</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>44532</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44539</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44557</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44557</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44559</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44559</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44559</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>44573</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44573</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44575</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44578</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44596</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44600</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44600</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44601</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>44607</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44613</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44615</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44621</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44624</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44624</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>44631</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44634</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44635</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44637</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44638</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44641</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44644</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44644</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44648</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44651</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44651</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>44651</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44651</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44655</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44659</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44659</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>44659</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44659</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44659</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44659</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44671</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44671</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44692</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44693</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44697</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44701</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44701</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44705</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44705</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44705</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44711</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44711</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44712</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44712</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44714</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44714</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44726</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44727</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44727</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44728</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44729</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44735</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44735</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44739</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44739</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44753</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44756</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44756</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44757</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44762</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44763</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44770</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44777</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44795</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>44796</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>44796</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44796</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44797</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44801</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>44812</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44813</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44813</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44818</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44823</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44823</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44830</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44830</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44834</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44834</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44847</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44847</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44851</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44851</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44865</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44865</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44866</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44867</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44872</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44872</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>44872</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44872</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44873</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44876</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44883</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44887</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44893</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44893</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44896</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44896</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44899</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44900</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44900</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44900</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44900</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44900</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44900</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44900</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44900</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44901</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44903</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44907</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44914</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44917</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>44926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44931</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>44950</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>44951</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>44953</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44958</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44958</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44964</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44965</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44967</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44970</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44970</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44974</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44974</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44974</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44974</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44981</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44990</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44995</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44995</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44999</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44999</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45002</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45002</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45013</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45014</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45019</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45019</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45019</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45019</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45020</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45027</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45027</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45027</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45028</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45030</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45030</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45035</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45035</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45040</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45042</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45044</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45051</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45051</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45058</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45061</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45061</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45062</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45062</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45062</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45063</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45070</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45070</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45070</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45075</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45084</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45084</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45085</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45089</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45091</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45091</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45092</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45092</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45096</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45097</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45097</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45097</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45098</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45098</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45104</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45104</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45104</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45104</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45109</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45109</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45109</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45110</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45110</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45110</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45117</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45118</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45126</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45128</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45131</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45132</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45132</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45145</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45145</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45145</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45149</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45153</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45153</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45154</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45155</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45155</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45159</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45159</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45159</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45162</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45162</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45162</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45162</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45162</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45163</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45163</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45163</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45166</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45167</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45167</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45167</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45168</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45168</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45169</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45169</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45170</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45170</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45170</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45176</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45176</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45181</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45182</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45182</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45182</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45186</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45190</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45190</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45190</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45190</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45194</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45194</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45198</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45199</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45199</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45203</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45204</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45204</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45205</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45205</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45211</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45211</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45218</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
         <v>45223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45225</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45225</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45226</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45225</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45229</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45229</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45229</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45229</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45229</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>45229</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45230</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45233</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45236</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45238</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45238</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45243</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45244</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45245</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45245</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45245</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45245</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>45245</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45245</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>45245</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45246</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45246</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45250</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45251</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45251</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45251</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45252</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45252</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45252</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45252</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45254</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>45254</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45254</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45254</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45254</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45254</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45254</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45254</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45254</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45254</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45257</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45257</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45257</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45257</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45258</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45259</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45259</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45260</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45265</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45267</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45268</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45268</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45271</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45272</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45274</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45274</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45278</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45279</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45281</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45281</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45287</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45288</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45293</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45293</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>45293</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45293</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45293</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45295</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45295</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45299</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45299</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45299</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45299</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45300</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45300</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45301</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45307</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45307</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45309</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45309</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45310</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>45314</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45314</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45315</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45316</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45316</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45316</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45316</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50720,14 +50720,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 4528-2024</t>
+          <t>A 4523-2024</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -50777,14 +50777,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 4523-2024</t>
+          <t>A 4527-2024</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -50834,14 +50834,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 4527-2024</t>
+          <t>A 4528-2024</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -50898,7 +50898,7 @@
         <v>45328</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45329</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45330</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45334</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51181,14 +51181,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 6779-2024</t>
+          <t>A 6793-2024</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 6793-2024</t>
+          <t>A 6779-2024</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -51312,7 +51312,7 @@
         <v>45342</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45343</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45344</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45344</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45348</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45348</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45350</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51714,14 +51714,14 @@
     <row r="888" ht="15" customHeight="1">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 8122-2024</t>
+          <t>A 8135-2024</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -51771,14 +51771,14 @@
     <row r="889" ht="15" customHeight="1">
       <c r="A889" t="inlineStr">
         <is>
-          <t>A 8140-2024</t>
+          <t>A 8128-2024</t>
         </is>
       </c>
       <c r="B889" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -51828,14 +51828,14 @@
     <row r="890" ht="15" customHeight="1">
       <c r="A890" t="inlineStr">
         <is>
-          <t>A 8128-2024</t>
+          <t>A 8122-2024</t>
         </is>
       </c>
       <c r="B890" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         </is>
       </c>
       <c r="G890" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -51882,62 +51882,580 @@
       </c>
       <c r="R890" s="2" t="inlineStr"/>
     </row>
-    <row r="891">
+    <row r="891" ht="15" customHeight="1">
       <c r="A891" t="inlineStr">
         <is>
-          <t>A 8135-2024</t>
+          <t>A 8140-2024</t>
         </is>
       </c>
       <c r="B891" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="C891" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G891" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H891" t="n">
+        <v>0</v>
+      </c>
+      <c r="I891" t="n">
+        <v>0</v>
+      </c>
+      <c r="J891" t="n">
+        <v>0</v>
+      </c>
+      <c r="K891" t="n">
+        <v>0</v>
+      </c>
+      <c r="L891" t="n">
+        <v>0</v>
+      </c>
+      <c r="M891" t="n">
+        <v>0</v>
+      </c>
+      <c r="N891" t="n">
+        <v>0</v>
+      </c>
+      <c r="O891" t="n">
+        <v>0</v>
+      </c>
+      <c r="P891" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q891" t="n">
+        <v>0</v>
+      </c>
+      <c r="R891" s="2" t="inlineStr"/>
+    </row>
+    <row r="892" ht="15" customHeight="1">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>A 8374-2024</t>
+        </is>
+      </c>
+      <c r="B892" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="C892" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="G892" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H892" t="n">
+        <v>0</v>
+      </c>
+      <c r="I892" t="n">
+        <v>0</v>
+      </c>
+      <c r="J892" t="n">
+        <v>0</v>
+      </c>
+      <c r="K892" t="n">
+        <v>0</v>
+      </c>
+      <c r="L892" t="n">
+        <v>0</v>
+      </c>
+      <c r="M892" t="n">
+        <v>0</v>
+      </c>
+      <c r="N892" t="n">
+        <v>0</v>
+      </c>
+      <c r="O892" t="n">
+        <v>0</v>
+      </c>
+      <c r="P892" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q892" t="n">
+        <v>0</v>
+      </c>
+      <c r="R892" s="2" t="inlineStr"/>
+    </row>
+    <row r="893" ht="15" customHeight="1">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>A 8293-2024</t>
+        </is>
+      </c>
+      <c r="B893" s="1" t="n">
         <v>45352</v>
       </c>
-      <c r="D891" t="inlineStr">
-        <is>
-          <t>HALLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E891" t="inlineStr">
-        <is>
-          <t>HYLTE</t>
-        </is>
-      </c>
-      <c r="G891" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H891" t="n">
-        <v>0</v>
-      </c>
-      <c r="I891" t="n">
-        <v>0</v>
-      </c>
-      <c r="J891" t="n">
-        <v>0</v>
-      </c>
-      <c r="K891" t="n">
-        <v>0</v>
-      </c>
-      <c r="L891" t="n">
-        <v>0</v>
-      </c>
-      <c r="M891" t="n">
-        <v>0</v>
-      </c>
-      <c r="N891" t="n">
-        <v>0</v>
-      </c>
-      <c r="O891" t="n">
-        <v>0</v>
-      </c>
-      <c r="P891" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q891" t="n">
-        <v>0</v>
-      </c>
-      <c r="R891" s="2" t="inlineStr"/>
+      <c r="C893" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G893" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H893" t="n">
+        <v>0</v>
+      </c>
+      <c r="I893" t="n">
+        <v>0</v>
+      </c>
+      <c r="J893" t="n">
+        <v>0</v>
+      </c>
+      <c r="K893" t="n">
+        <v>0</v>
+      </c>
+      <c r="L893" t="n">
+        <v>0</v>
+      </c>
+      <c r="M893" t="n">
+        <v>0</v>
+      </c>
+      <c r="N893" t="n">
+        <v>0</v>
+      </c>
+      <c r="O893" t="n">
+        <v>0</v>
+      </c>
+      <c r="P893" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q893" t="n">
+        <v>0</v>
+      </c>
+      <c r="R893" s="2" t="inlineStr"/>
+    </row>
+    <row r="894" ht="15" customHeight="1">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>A 8298-2024</t>
+        </is>
+      </c>
+      <c r="B894" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C894" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G894" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H894" t="n">
+        <v>0</v>
+      </c>
+      <c r="I894" t="n">
+        <v>0</v>
+      </c>
+      <c r="J894" t="n">
+        <v>0</v>
+      </c>
+      <c r="K894" t="n">
+        <v>0</v>
+      </c>
+      <c r="L894" t="n">
+        <v>0</v>
+      </c>
+      <c r="M894" t="n">
+        <v>0</v>
+      </c>
+      <c r="N894" t="n">
+        <v>0</v>
+      </c>
+      <c r="O894" t="n">
+        <v>0</v>
+      </c>
+      <c r="P894" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q894" t="n">
+        <v>0</v>
+      </c>
+      <c r="R894" s="2" t="inlineStr"/>
+    </row>
+    <row r="895" ht="15" customHeight="1">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>A 8351-2024</t>
+        </is>
+      </c>
+      <c r="B895" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C895" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G895" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H895" t="n">
+        <v>0</v>
+      </c>
+      <c r="I895" t="n">
+        <v>0</v>
+      </c>
+      <c r="J895" t="n">
+        <v>0</v>
+      </c>
+      <c r="K895" t="n">
+        <v>0</v>
+      </c>
+      <c r="L895" t="n">
+        <v>0</v>
+      </c>
+      <c r="M895" t="n">
+        <v>0</v>
+      </c>
+      <c r="N895" t="n">
+        <v>0</v>
+      </c>
+      <c r="O895" t="n">
+        <v>0</v>
+      </c>
+      <c r="P895" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q895" t="n">
+        <v>0</v>
+      </c>
+      <c r="R895" s="2" t="inlineStr"/>
+    </row>
+    <row r="896" ht="15" customHeight="1">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>A 8287-2024</t>
+        </is>
+      </c>
+      <c r="B896" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C896" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G896" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H896" t="n">
+        <v>0</v>
+      </c>
+      <c r="I896" t="n">
+        <v>0</v>
+      </c>
+      <c r="J896" t="n">
+        <v>0</v>
+      </c>
+      <c r="K896" t="n">
+        <v>0</v>
+      </c>
+      <c r="L896" t="n">
+        <v>0</v>
+      </c>
+      <c r="M896" t="n">
+        <v>0</v>
+      </c>
+      <c r="N896" t="n">
+        <v>0</v>
+      </c>
+      <c r="O896" t="n">
+        <v>0</v>
+      </c>
+      <c r="P896" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q896" t="n">
+        <v>0</v>
+      </c>
+      <c r="R896" s="2" t="inlineStr"/>
+    </row>
+    <row r="897" ht="15" customHeight="1">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>A 8301-2024</t>
+        </is>
+      </c>
+      <c r="B897" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C897" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G897" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H897" t="n">
+        <v>0</v>
+      </c>
+      <c r="I897" t="n">
+        <v>0</v>
+      </c>
+      <c r="J897" t="n">
+        <v>0</v>
+      </c>
+      <c r="K897" t="n">
+        <v>0</v>
+      </c>
+      <c r="L897" t="n">
+        <v>0</v>
+      </c>
+      <c r="M897" t="n">
+        <v>0</v>
+      </c>
+      <c r="N897" t="n">
+        <v>0</v>
+      </c>
+      <c r="O897" t="n">
+        <v>0</v>
+      </c>
+      <c r="P897" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q897" t="n">
+        <v>0</v>
+      </c>
+      <c r="R897" s="2" t="inlineStr"/>
+    </row>
+    <row r="898" ht="15" customHeight="1">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>A 8305-2024</t>
+        </is>
+      </c>
+      <c r="B898" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C898" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G898" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H898" t="n">
+        <v>0</v>
+      </c>
+      <c r="I898" t="n">
+        <v>0</v>
+      </c>
+      <c r="J898" t="n">
+        <v>0</v>
+      </c>
+      <c r="K898" t="n">
+        <v>0</v>
+      </c>
+      <c r="L898" t="n">
+        <v>0</v>
+      </c>
+      <c r="M898" t="n">
+        <v>0</v>
+      </c>
+      <c r="N898" t="n">
+        <v>0</v>
+      </c>
+      <c r="O898" t="n">
+        <v>0</v>
+      </c>
+      <c r="P898" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q898" t="n">
+        <v>0</v>
+      </c>
+      <c r="R898" s="2" t="inlineStr"/>
+    </row>
+    <row r="899" ht="15" customHeight="1">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>A 8318-2024</t>
+        </is>
+      </c>
+      <c r="B899" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C899" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G899" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H899" t="n">
+        <v>0</v>
+      </c>
+      <c r="I899" t="n">
+        <v>0</v>
+      </c>
+      <c r="J899" t="n">
+        <v>0</v>
+      </c>
+      <c r="K899" t="n">
+        <v>0</v>
+      </c>
+      <c r="L899" t="n">
+        <v>0</v>
+      </c>
+      <c r="M899" t="n">
+        <v>0</v>
+      </c>
+      <c r="N899" t="n">
+        <v>0</v>
+      </c>
+      <c r="O899" t="n">
+        <v>0</v>
+      </c>
+      <c r="P899" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q899" t="n">
+        <v>0</v>
+      </c>
+      <c r="R899" s="2" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>A 8353-2024</t>
+        </is>
+      </c>
+      <c r="B900" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C900" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>HALLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>HYLTE</t>
+        </is>
+      </c>
+      <c r="G900" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H900" t="n">
+        <v>0</v>
+      </c>
+      <c r="I900" t="n">
+        <v>0</v>
+      </c>
+      <c r="J900" t="n">
+        <v>0</v>
+      </c>
+      <c r="K900" t="n">
+        <v>0</v>
+      </c>
+      <c r="L900" t="n">
+        <v>0</v>
+      </c>
+      <c r="M900" t="n">
+        <v>0</v>
+      </c>
+      <c r="N900" t="n">
+        <v>0</v>
+      </c>
+      <c r="O900" t="n">
+        <v>0</v>
+      </c>
+      <c r="P900" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q900" t="n">
+        <v>0</v>
+      </c>
+      <c r="R900" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -569,7 +569,7 @@
         <v>43986</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>44873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>43923</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>43769</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>44693</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>43342</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>43467</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>43983</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44332</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44601</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45245</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45343</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>43319</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>43348</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>43374</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>43409</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>43413</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>43413</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>43413</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>43415</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>43415</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>43415</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43418</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43419</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43420</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43420</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43423</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43423</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43425</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43431</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43432</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43432</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43432</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43432</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43432</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>43433</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>43433</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>43433</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>43433</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>43437</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>43437</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43437</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>43437</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>43437</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>43441</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>43441</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>43445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>43447</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>43447</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>43447</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>43454</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>43467</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>43467</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>43467</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>43467</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>43468</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>43468</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>43468</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>43472</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>43472</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>43472</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>43473</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>43473</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>43473</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>43475</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>43475</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>43475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>43476</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>43479</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43479</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>43482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>43503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>43505</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43516</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43516</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43516</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43516</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43516</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43521</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43524</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43528</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43535</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43536</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43536</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43542</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43542</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43542</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43544</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43545</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43545</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43549</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43549</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43550</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43550</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43552</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43552</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43553</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43557</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43558</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43558</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43563</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43564</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43564</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43565</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43566</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43570</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43573</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>43581</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>43584</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>43587</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>43606</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>43612</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43612</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>43612</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>43616</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>43619</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>43620</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>43620</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>43656</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>43658</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>43663</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>43664</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>43665</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>43665</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>43668</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>43668</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>43668</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>43682</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>43682</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>43682</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43705</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43706</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43712</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43712</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43712</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43731</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43731</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43732</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43732</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43738</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43739</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43739</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43742</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43742</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43742</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43768</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43770</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43774</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43775</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43775</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43775</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43790</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43803</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43837</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43837</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43839</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43839</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43846</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43850</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43854</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43858</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43859</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>43871</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>43871</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43875</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43880</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43880</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43886</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>43901</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>43901</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>43901</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>43903</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>43903</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>43908</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43908</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43913</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43916</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43916</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43927</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43936</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43937</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43937</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>43941</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>43943</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>43943</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>43949</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43957</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43957</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43966</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43969</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43983</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43983</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43983</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43983</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44000</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44007</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44019</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44020</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44020</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44020</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44021</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44021</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44022</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44022</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44025</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44028</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44036</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44039</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44041</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44041</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44043</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44046</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44055</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44060</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44062</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44092</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44095</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44095</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44095</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44103</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44107</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44122</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44122</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44123</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44123</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44124</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44132</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44133</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>44140</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44140</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44141</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44144</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44145</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44146</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44146</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44147</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44147</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44147</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44147</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44147</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44154</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44159</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44159</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44166</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44168</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44172</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44173</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44174</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44174</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44177</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44177</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44180</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>44187</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44193</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44199</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44210</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44216</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44221</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44224</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44230</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44230</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44231</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44236</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44236</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44236</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44238</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44242</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44243</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44245</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44245</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44250</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44250</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44251</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44256</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44261</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44263</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44263</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44265</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44266</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44266</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44266</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44266</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44267</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44267</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44267</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44267</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44267</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44274</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44274</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44274</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44277</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44277</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44278</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44281</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44293</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44293</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44295</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44298</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44298</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44302</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44306</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44307</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44321</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44322</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44322</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44323</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44332</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44335</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44336</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44336</v>
       </c>
       <c r="C344" s="1" t="n">
-     